--- a/dataset_t6_grouped/results2/G4/G4_T3603_W0074F0003T0006Z000C1N75_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3603_W0074F0003T0006Z000C1N75_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>14.25121663848233</v>
+        <v>2.315822703753378</v>
       </c>
       <c r="D2" t="n">
-        <v>13.94947264916403</v>
+        <v>2.266789305489155</v>
       </c>
       <c r="E2" t="n">
-        <v>16.38212135327791</v>
+        <v>2.66209471990766</v>
       </c>
       <c r="F2" t="n">
-        <v>15.62140960379576</v>
+        <v>2.538479060616811</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>37.10147864850656</v>
+        <v>6.028990280382316</v>
       </c>
       <c r="D3" t="n">
-        <v>36.8749640435955</v>
+        <v>5.99218165708427</v>
       </c>
       <c r="E3" t="n">
-        <v>16.38212135327791</v>
+        <v>2.66209471990766</v>
       </c>
       <c r="F3" t="n">
-        <v>15.62140960379576</v>
+        <v>2.538479060616811</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>30.10398644698074</v>
+        <v>4.89189779763437</v>
       </c>
       <c r="D4" t="n">
-        <v>19.94102086032723</v>
+        <v>3.240415889803175</v>
       </c>
       <c r="E4" t="n">
-        <v>16.38212135327791</v>
+        <v>2.66209471990766</v>
       </c>
       <c r="F4" t="n">
-        <v>15.62140960379576</v>
+        <v>2.538479060616811</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>25.6658951183009</v>
+        <v>4.170707956723897</v>
       </c>
       <c r="D5" t="n">
-        <v>6.677570938080378</v>
+        <v>1.085105277438061</v>
       </c>
       <c r="E5" t="n">
-        <v>16.38212135327791</v>
+        <v>2.66209471990766</v>
       </c>
       <c r="F5" t="n">
-        <v>15.62140960379576</v>
+        <v>2.538479060616811</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>46.97073557013984</v>
+        <v>7.632744530147724</v>
       </c>
       <c r="D6" t="n">
-        <v>27.55513270868117</v>
+        <v>4.477709065160691</v>
       </c>
       <c r="E6" t="n">
-        <v>16.38212135327791</v>
+        <v>2.66209471990766</v>
       </c>
       <c r="F6" t="n">
-        <v>15.62140960379576</v>
+        <v>2.538479060616811</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>31.20768520922616</v>
+        <v>5.071248846499251</v>
       </c>
       <c r="D7" t="n">
-        <v>57.87916697722389</v>
+        <v>9.405364633798882</v>
       </c>
       <c r="E7" t="n">
-        <v>16.38212135327791</v>
+        <v>2.66209471990766</v>
       </c>
       <c r="F7" t="n">
-        <v>15.62140960379576</v>
+        <v>2.538479060616811</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>67.24962569233699</v>
+        <v>10.92806417500476</v>
       </c>
       <c r="D8" t="n">
-        <v>40.0898989771738</v>
+        <v>6.514608583790742</v>
       </c>
       <c r="E8" t="n">
-        <v>16.38212135327791</v>
+        <v>2.66209471990766</v>
       </c>
       <c r="F8" t="n">
-        <v>15.62140960379576</v>
+        <v>2.538479060616811</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>57.76190098656557</v>
+        <v>9.386308910316906</v>
       </c>
       <c r="D9" t="n">
-        <v>40.91210089936718</v>
+        <v>6.648216396147166</v>
       </c>
       <c r="E9" t="n">
-        <v>16.38212135327791</v>
+        <v>2.66209471990766</v>
       </c>
       <c r="F9" t="n">
-        <v>15.62140960379576</v>
+        <v>2.538479060616811</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
